--- a/data/trans_bre/IP16_n_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 25,81</t>
+          <t>-21,85; 23,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 30,03</t>
+          <t>-4,52; 30,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 4,19</t>
+          <t>-46,24; 3,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 8,63</t>
+          <t>-50,98; 6,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 150,02</t>
+          <t>-53,08; 132,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 1017,07</t>
+          <t>-46,44; 874,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-95,71; 40,2</t>
+          <t>-100,0; 23,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 12,3</t>
+          <t>-12,14; 12,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 13,73</t>
+          <t>-4,35; 14,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 6,53</t>
+          <t>-10,38; 7,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 4,31</t>
+          <t>-25,79; 5,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 34,95</t>
+          <t>-25,44; 35,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 141,42</t>
+          <t>-24,93; 132,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 63,23</t>
+          <t>-51,7; 68,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,71; 14,23</t>
+          <t>-64,12; 14,55</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 10,2</t>
+          <t>-31,32; 7,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 12,6</t>
+          <t>-13,49; 12,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 21,1</t>
+          <t>-6,9; 20,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 26,32</t>
+          <t>-9,54; 26,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 34,14</t>
+          <t>-66,17; 26,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,5; 188,17</t>
+          <t>-70,29; 177,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 692,26</t>
+          <t>-61,44; 630,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 137,12</t>
+          <t>-24,5; 126,64</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 7,87</t>
+          <t>-11,4; 8,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 11,17</t>
+          <t>-2,75; 11,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 5,62</t>
+          <t>-8,71; 5,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 5,33</t>
+          <t>-18,82; 4,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 22,34</t>
+          <t>-25,38; 23,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 102,95</t>
+          <t>-17,52; 110,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 57,72</t>
+          <t>-50,38; 45,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 17,77</t>
+          <t>-48,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-19,95</t>
+          <t>-18,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-57,3%</t>
+          <t>-47,01%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 23,69</t>
+          <t>-21,66; 26,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 30,07</t>
+          <t>-4,23; 29,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 3,64</t>
+          <t>-41,25; 3,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 6,18</t>
+          <t>-47,18; 14,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 132,12</t>
+          <t>-51,22; 159,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 874,49</t>
+          <t>-40,8; 956,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 23,39</t>
+          <t>-87,06; 105,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-23,47%</t>
+          <t>-2,76%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 12,87</t>
+          <t>-12,56; 12,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 14,23</t>
+          <t>-4,81; 13,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 7,17</t>
+          <t>-9,55; 7,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 5,28</t>
+          <t>-12,13; 9,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 35,71</t>
+          <t>-26,25; 34,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 132,82</t>
+          <t>-28,73; 129,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 68,26</t>
+          <t>-50,13; 71,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 14,55</t>
+          <t>-30,64; 34,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 7,75</t>
+          <t>-29,1; 8,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 12,59</t>
+          <t>-15,02; 11,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 20,84</t>
+          <t>-7,86; 19,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 26,15</t>
+          <t>-6,39; 28,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 26,99</t>
+          <t>-64,2; 28,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,29; 177,83</t>
+          <t>-66,64; 169,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,44; 630,11</t>
+          <t>-67,86; 565,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 126,64</t>
+          <t>-16,51; 141,49</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 8,25</t>
+          <t>-11,31; 7,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,66</t>
+          <t>-3,18; 10,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,35</t>
+          <t>-8,63; 5,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 4,52</t>
+          <t>-9,03; 9,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 23,09</t>
+          <t>-25,69; 21,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 110,75</t>
+          <t>-18,56; 101,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 45,66</t>
+          <t>-50,61; 55,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 14,21</t>
+          <t>-23,51; 31,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11,89</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-12,36</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-18,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>118,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-77,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-47,01%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.8749051581751488</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.365924087369153</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.092513110142138</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.226325171482181</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1214311613420499</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.599014122094776</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.5349082436529868</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5397227016365628</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-21,66; 26,26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,23; 29,63</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-41,25; 3,66</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-47,18; 14,59</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-51,22; 159,7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-40,8; 956,98</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-87,06; 105,96</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.876421462455468</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.7568318645520778</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.507318460353424</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.64993830739228</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5575911767283047</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4331611931102339</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.8960539826535605</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.71043298368866</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.33189911909809</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.895652888392813</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.523272442408467</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.676659429560045</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>13.56307230602278</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>0.7949061507830959</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,52</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-10,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-2,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-12,56; 12,37</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,81; 13,89</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,55; 7,45</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-12,13; 9,97</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-26,25; 34,15</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-28,73; 129,36</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-50,13; 71,26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-30,64; 34,87</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.4924375723705965</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7493885137004074</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2780988097103566</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.6347773991813923</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.06364922275961668</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2568262210326123</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1048870542474955</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.08075711515735461</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-11,81</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,51</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,03</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-29,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-6,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32,98%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.313501156633853</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.194943427711009</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.002556583296106</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.546433019747487</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2581756219607211</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3173272837830856</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5735872333289033</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3759709906482005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-29,1; 8,55</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-15,02; 11,59</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,86; 19,46</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,39; 28,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-64,2; 28,1</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-66,64; 169,8</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-67,86; 565,5</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-16,51; 141,49</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.608066817563572</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.814848062570268</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.22424426032861</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.394585905153789</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5752556743115412</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.386741631536783</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7104037691458646</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.371180924884546</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-9,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.267415558432818</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3842535326170758</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.034259177893567</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.143386765800693</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5906581269140401</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1170929988286804</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.7350109568207978</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.4035242664870249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-11,31; 7,95</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 10,68</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,63; 5,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-9,03; 9,45</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-25,69; 21,86</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-18,56; 101,71</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-50,61; 55,0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-23,51; 31,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.841924312471328</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.515717543367335</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.108117729637788</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.110011587576909</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8048465968656441</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7244569290681071</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.697178140856078</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3287355354032191</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-1.022816788929206</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.697006866545303</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.522735167322467</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.751789041440434</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.109298331378918</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.669161758229238</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>7.640151420325173</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.671450081855705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.8925325543245863</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8136443925664337</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.01208570152467746</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.08180828400468076</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1125303332482478</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2798644141450999</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.005295870280581951</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.01023745464737872</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.027689954802277</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.6997766368523524</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.22317471121803</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.518692284719393</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3299541874830652</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2069946378959247</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4327395411556695</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2724147626685718</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.486204826301203</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.428353884164705</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.18784936892884</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.734907817399575</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2189548305189426</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.103775843922363</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7238265048067668</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3970222682613186</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
